--- a/prisliste.xlsx
+++ b/prisliste.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3fa017e0d854f10e/Dokumenter/NTNUI Klubbklær/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3fa017e0d854f10e/Dokumenter/NTNUI Klubbklær/NTNUI-klubbklar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{B4ED0D05-E1B3-4E84-874F-66883491099E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A72CDF2-4BFB-4818-BE51-B5621362E0A2}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{B4ED0D05-E1B3-4E84-874F-66883491099E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{798BA98F-17AF-4B65-94E7-E57D6BA37BC0}"/>
   <bookViews>
-    <workbookView xWindow="8370" yWindow="1995" windowWidth="28800" windowHeight="15345" xr2:uid="{DF4A07A9-01BB-4626-8F05-0D7593CD8052}"/>
+    <workbookView minimized="1" xWindow="5780" yWindow="5780" windowWidth="2370" windowHeight="560" xr2:uid="{DF4A07A9-01BB-4626-8F05-0D7593CD8052}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Overtrekksjakke</t>
   </si>
@@ -74,15 +74,9 @@
     <t>Joggebukse</t>
   </si>
   <si>
-    <t>Hverdagsgenser</t>
-  </si>
-  <si>
     <t>Bag (38 L)</t>
   </si>
   <si>
-    <t>Sekk (65 L)</t>
-  </si>
-  <si>
     <t>Sleeves</t>
   </si>
   <si>
@@ -95,14 +89,23 @@
     <t xml:space="preserve"> Klubbkolleksjonen 25</t>
   </si>
   <si>
-    <t>Prisliste</t>
+    <t>Pris uten navn</t>
+  </si>
+  <si>
+    <t>Pris med navn</t>
+  </si>
+  <si>
+    <t>Tynn genser (bomull)</t>
+  </si>
+  <si>
+    <t>Bag (65 L)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,12 +129,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -169,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -276,26 +273,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -303,26 +285,17 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -665,174 +638,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3EDE4B1-03FF-4354-A8BD-BFB242BF1228}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="65.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" ht="65.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="11"/>
-    </row>
-    <row r="2" spans="1:3" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>800</v>
-      </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>740</v>
+      </c>
+      <c r="C2" s="3">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2">
         <v>600</v>
       </c>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2">
         <v>196</v>
       </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2">
         <v>351</v>
       </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2">
         <v>422</v>
       </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2">
         <v>367</v>
       </c>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>453</v>
       </c>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2">
         <v>335</v>
       </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>188</v>
       </c>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2">
         <v>259</v>
       </c>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>279</v>
       </c>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2">
         <v>193</v>
       </c>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="5">
-        <v>0</v>
-      </c>
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4">
+        <v>391</v>
+      </c>
+      <c r="C14" s="3">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2">
         <v>829</v>
       </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="5">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4">
         <v>179</v>
       </c>
-      <c r="C16" s="6"/>
-    </row>
-    <row r="17" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2">
         <v>321</v>
       </c>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="8">
+      <c r="C17" s="2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6">
         <v>356</v>
       </c>
-      <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="C18" s="6">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
